--- a/assets/infobasica/planilhas/aula05_nivel3.xlsx
+++ b/assets/infobasica/planilhas/aula05_nivel3.xlsx
@@ -532,7 +532,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Orçamento de piso: preço do m² em E2 e, em F2, =C21,1E2 (área com 10% de perda × preço), formatado como moeda.</t>
+          <t>Orçamento de piso: preço do m² em E2 e, em F2, =C2*1,1*E2 (área com 10% de perda × preço), formatado como moeda.</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Para abrir no Google Planilhas: Google Drive → Novo → Upload de arquivo; depois clique no arquivo → Abrir com → Planilhas Google.</t>
+          <t>Esta é a sua cópia: altere à vontade.</t>
         </is>
       </c>
     </row>
